--- a/_experimentalData/e4WatchData/featureAnalysisExcel/20240924_Ruixiao_FeatureExcelData/Acceleration_Baseline_normalized_windowed_features.xlsx
+++ b/_experimentalData/e4WatchData/featureAnalysisExcel/20240924_Ruixiao_FeatureExcelData/Acceleration_Baseline_normalized_windowed_features.xlsx
@@ -438,42 +438,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Standard Deviation</t>
+          <t>std</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Kurtosis</t>
+          <t>kurtosis</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Skewness</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Zero Crossing Rate</t>
+          <t>zcr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>entropy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Band Energy (2-3 Hz)</t>
+          <t>band_energy</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Spectral Flux</t>
+          <t>spectral_flux</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="B3" t="n">
         <v>0.616057105759765</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="B4" t="n">
         <v>0.7335900794463441</v>
@@ -566,7 +566,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15</v>
+        <v>11.25</v>
       </c>
       <c r="B5" t="n">
         <v>0.8047426732558023</v>
@@ -595,7 +595,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
         <v>0.792299972794055</v>
@@ -624,7 +624,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>18.75</v>
       </c>
       <c r="B7" t="n">
         <v>0.8218192487149025</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="B8" t="n">
         <v>0.761888312722391</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35</v>
+        <v>26.25</v>
       </c>
       <c r="B9" t="n">
         <v>0.752865292666641</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B10" t="n">
         <v>0.7099512238261241</v>
@@ -740,7 +740,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>45</v>
+        <v>33.75</v>
       </c>
       <c r="B11" t="n">
         <v>0.6338338969350872</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="B12" t="n">
         <v>0.5920485450849071</v>
@@ -798,7 +798,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55</v>
+        <v>41.25</v>
       </c>
       <c r="B13" t="n">
         <v>0.5585166869296216</v>
@@ -827,7 +827,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B14" t="n">
         <v>0.5890562665522907</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>65</v>
+        <v>48.75</v>
       </c>
       <c r="B15" t="n">
         <v>0.6383324091656277</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>70</v>
+        <v>52.5</v>
       </c>
       <c r="B16" t="n">
         <v>0.6476538592155237</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>75</v>
+        <v>56.25</v>
       </c>
       <c r="B17" t="n">
         <v>0.5613409444574131</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B18" t="n">
         <v>0.5521118150935536</v>
@@ -972,7 +972,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>85</v>
+        <v>63.75</v>
       </c>
       <c r="B19" t="n">
         <v>0.6784329676822694</v>
@@ -1001,7 +1001,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>90</v>
+        <v>67.5</v>
       </c>
       <c r="B20" t="n">
         <v>0.7510887235734316</v>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95</v>
+        <v>71.25</v>
       </c>
       <c r="B21" t="n">
         <v>0.8710412537600973</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="B22" t="n">
         <v>0.9715192269674446</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>105</v>
+        <v>78.75</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110</v>
+        <v>82.5</v>
       </c>
       <c r="B24" t="n">
         <v>0.8417238535752745</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115</v>
+        <v>86.25</v>
       </c>
       <c r="B25" t="n">
         <v>0.475048378553609</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B26" t="n">
         <v>0.254637583015537</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125</v>
+        <v>93.75</v>
       </c>
       <c r="B27" t="n">
         <v>0.372272453541143</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130</v>
+        <v>97.5</v>
       </c>
       <c r="B28" t="n">
         <v>0.3207234258804448</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135</v>
+        <v>101.25</v>
       </c>
       <c r="B29" t="n">
         <v>0.3927657478259192</v>
@@ -1291,7 +1291,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B30" t="n">
         <v>0.4563928376737323</v>
@@ -1320,7 +1320,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>145</v>
+        <v>108.75</v>
       </c>
       <c r="B31" t="n">
         <v>0.3911753766381878</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>150</v>
+        <v>112.5</v>
       </c>
       <c r="B32" t="n">
         <v>0.3815233650107075</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>155</v>
+        <v>116.25</v>
       </c>
       <c r="B33" t="n">
         <v>0.5364540427357696</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="B34" t="n">
         <v>0.7301579738282982</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>165</v>
+        <v>123.75</v>
       </c>
       <c r="B35" t="n">
         <v>0.901705415552243</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>170</v>
+        <v>127.5</v>
       </c>
       <c r="B36" t="n">
         <v>0.9157744391728215</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>175</v>
+        <v>131.25</v>
       </c>
       <c r="B37" t="n">
         <v>0.9645165903119022</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="B38" t="n">
         <v>0.7907698340650455</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>185</v>
+        <v>138.75</v>
       </c>
       <c r="B39" t="n">
         <v>0.7265398588557872</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>190</v>
+        <v>142.5</v>
       </c>
       <c r="B40" t="n">
         <v>0.8248845589219087</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>195</v>
+        <v>146.25</v>
       </c>
       <c r="B41" t="n">
         <v>0.7930688866734528</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B42" t="n">
         <v>0.858450472877621</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>205</v>
+        <v>153.75</v>
       </c>
       <c r="B43" t="n">
         <v>0.9860074452369219</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>210</v>
+        <v>157.5</v>
       </c>
       <c r="B44" t="n">
         <v>0.9589454967210997</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>215</v>
+        <v>161.25</v>
       </c>
       <c r="B45" t="n">
         <v>0.9869971879615207</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="B46" t="n">
         <v>0.978404616286241</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>225</v>
+        <v>168.75</v>
       </c>
       <c r="B47" t="n">
         <v>0.9540996085992646</v>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>230</v>
+        <v>172.5</v>
       </c>
       <c r="B48" t="n">
         <v>0.920755338607421</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>235</v>
+        <v>176.25</v>
       </c>
       <c r="B49" t="n">
         <v>0.9526160331838298</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B50" t="n">
         <v>0.814034100343406</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>245</v>
+        <v>183.75</v>
       </c>
       <c r="B51" t="n">
         <v>0.7721429345957773</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>250</v>
+        <v>187.5</v>
       </c>
       <c r="B52" t="n">
         <v>0.8496412697033549</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>255</v>
+        <v>191.25</v>
       </c>
       <c r="B53" t="n">
         <v>0.7914398635656568</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="B54" t="n">
         <v>0.7965804117651203</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>265</v>
+        <v>198.75</v>
       </c>
       <c r="B55" t="n">
         <v>0.8190428398278016</v>
@@ -2045,7 +2045,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>270</v>
+        <v>202.5</v>
       </c>
       <c r="B56" t="n">
         <v>0.7671748657418078</v>
@@ -2074,7 +2074,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>275</v>
+        <v>206.25</v>
       </c>
       <c r="B57" t="n">
         <v>0.812582910992603</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="B58" t="n">
         <v>0.921570467799242</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>285</v>
+        <v>213.75</v>
       </c>
       <c r="B59" t="n">
         <v>0.8534349163862913</v>
@@ -2161,7 +2161,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>290</v>
+        <v>217.5</v>
       </c>
       <c r="B60" t="n">
         <v>0.8825038837282193</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>295</v>
+        <v>221.25</v>
       </c>
       <c r="B61" t="n">
         <v>0.7664545857688694</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B62" t="n">
         <v>0.7768757770538315</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>305</v>
+        <v>228.75</v>
       </c>
       <c r="B63" t="n">
         <v>0.7759218254881546</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>310</v>
+        <v>232.5</v>
       </c>
       <c r="B64" t="n">
         <v>0.7478631437450218</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>315</v>
+        <v>236.25</v>
       </c>
       <c r="B65" t="n">
         <v>0.693115776546378</v>
@@ -2335,7 +2335,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="B66" t="n">
         <v>0.6395694381230896</v>
@@ -2364,7 +2364,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>325</v>
+        <v>243.75</v>
       </c>
       <c r="B67" t="n">
         <v>0.5166577708242528</v>
@@ -2393,7 +2393,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>330</v>
+        <v>247.5</v>
       </c>
       <c r="B68" t="n">
         <v>0.4967503533993494</v>
@@ -2422,7 +2422,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>335</v>
+        <v>251.25</v>
       </c>
       <c r="B69" t="n">
         <v>0.3027602218330685</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>340</v>
+        <v>255</v>
       </c>
       <c r="B70" t="n">
         <v>0.4295430359217818</v>
@@ -2480,7 +2480,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>345</v>
+        <v>258.75</v>
       </c>
       <c r="B71" t="n">
         <v>0.5129603205612767</v>
@@ -2509,7 +2509,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>350</v>
+        <v>262.5</v>
       </c>
       <c r="B72" t="n">
         <v>0.4981339310930792</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>355</v>
+        <v>266.25</v>
       </c>
       <c r="B73" t="n">
         <v>0.5231392619478612</v>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="B74" t="n">
         <v>0.4526573731580328</v>
@@ -2596,7 +2596,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>365</v>
+        <v>273.75</v>
       </c>
       <c r="B75" t="n">
         <v>0.4459580645022072</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>370</v>
+        <v>277.5</v>
       </c>
       <c r="B76" t="n">
         <v>0.4210753825718854</v>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>375</v>
+        <v>281.25</v>
       </c>
       <c r="B77" t="n">
         <v>0.4827770425531526</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="B78" t="n">
         <v>0.5268679132446437</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>385</v>
+        <v>288.75</v>
       </c>
       <c r="B79" t="n">
         <v>0.5536770445622636</v>
@@ -2741,7 +2741,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>390</v>
+        <v>292.5</v>
       </c>
       <c r="B80" t="n">
         <v>0.4768230765203896</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>395</v>
+        <v>296.25</v>
       </c>
       <c r="B81" t="n">
         <v>0.5378754428865875</v>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B82" t="n">
         <v>0.5284632660799105</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>405</v>
+        <v>303.75</v>
       </c>
       <c r="B83" t="n">
         <v>0.4765514930845001</v>
@@ -2857,7 +2857,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>410</v>
+        <v>307.5</v>
       </c>
       <c r="B84" t="n">
         <v>0.4119453737633449</v>
@@ -2886,7 +2886,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>415</v>
+        <v>311.25</v>
       </c>
       <c r="B85" t="n">
         <v>0.4797690496926066</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="B86" t="n">
         <v>0.4059413550500466</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>425</v>
+        <v>318.75</v>
       </c>
       <c r="B87" t="n">
         <v>0.4737333487440338</v>
@@ -2973,7 +2973,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>430</v>
+        <v>322.5</v>
       </c>
       <c r="B88" t="n">
         <v>0.3824423320006218</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>435</v>
+        <v>326.25</v>
       </c>
       <c r="B89" t="n">
         <v>0.4164637720383126</v>
@@ -3031,7 +3031,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="B90" t="n">
         <v>0.420555651587776</v>
@@ -3060,7 +3060,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>445</v>
+        <v>333.75</v>
       </c>
       <c r="B91" t="n">
         <v>0.3748219793500454</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>450</v>
+        <v>337.5</v>
       </c>
       <c r="B92" t="n">
         <v>0.4324891572301368</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>455</v>
+        <v>341.25</v>
       </c>
       <c r="B93" t="n">
         <v>0.4400516140660358</v>
@@ -3147,7 +3147,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>460</v>
+        <v>345</v>
       </c>
       <c r="B94" t="n">
         <v>0.3431885249808175</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>465</v>
+        <v>348.75</v>
       </c>
       <c r="B95" t="n">
         <v>0.4745746755796887</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>470</v>
+        <v>352.5</v>
       </c>
       <c r="B96" t="n">
         <v>0.3974654731585048</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>475</v>
+        <v>356.25</v>
       </c>
       <c r="B97" t="n">
         <v>0.4242680297342503</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="B98" t="n">
         <v>0.4624053841752982</v>
@@ -3292,7 +3292,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>485</v>
+        <v>363.75</v>
       </c>
       <c r="B99" t="n">
         <v>0.433975436546973</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>490</v>
+        <v>367.5</v>
       </c>
       <c r="B100" t="n">
         <v>0.4443556712850523</v>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>495</v>
+        <v>371.25</v>
       </c>
       <c r="B101" t="n">
         <v>0.4679654810984459</v>
@@ -3379,7 +3379,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="B102" t="n">
         <v>0.4513701118090552</v>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>505</v>
+        <v>378.75</v>
       </c>
       <c r="B103" t="n">
         <v>0.4660369685232837</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>510</v>
+        <v>382.5</v>
       </c>
       <c r="B104" t="n">
         <v>0.4515248944914845</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>515</v>
+        <v>386.25</v>
       </c>
       <c r="B105" t="n">
         <v>0.3567808627420419</v>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>520</v>
+        <v>390</v>
       </c>
       <c r="B106" t="n">
         <v>0.4047182877136635</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>525</v>
+        <v>393.75</v>
       </c>
       <c r="B107" t="n">
         <v>0.440960075257351</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>530</v>
+        <v>397.5</v>
       </c>
       <c r="B108" t="n">
         <v>0.5290127258408859</v>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>535</v>
+        <v>401.25</v>
       </c>
       <c r="B109" t="n">
         <v>0.5105539356807611</v>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>540</v>
+        <v>405</v>
       </c>
       <c r="B110" t="n">
         <v>0.4259042113597076</v>
@@ -3640,7 +3640,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>545</v>
+        <v>408.75</v>
       </c>
       <c r="B111" t="n">
         <v>0.3936984796857956</v>
@@ -3669,7 +3669,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>550</v>
+        <v>412.5</v>
       </c>
       <c r="B112" t="n">
         <v>0.3869599683195446</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>555</v>
+        <v>416.25</v>
       </c>
       <c r="B113" t="n">
         <v>0.449378484944674</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="B114" t="n">
         <v>0.5101065101100488</v>
@@ -3756,7 +3756,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>565</v>
+        <v>423.75</v>
       </c>
       <c r="B115" t="n">
         <v>0.443043741248232</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>570</v>
+        <v>427.5</v>
       </c>
       <c r="B116" t="n">
         <v>0.5908128734806581</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>575</v>
+        <v>431.25</v>
       </c>
       <c r="B117" t="n">
         <v>0.6122224751642733</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>580</v>
+        <v>435</v>
       </c>
       <c r="B118" t="n">
         <v>0.4686175645435355</v>
@@ -3872,7 +3872,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>585</v>
+        <v>438.75</v>
       </c>
       <c r="B119" t="n">
         <v>0.4623475443662954</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>590</v>
+        <v>442.5</v>
       </c>
       <c r="B120" t="n">
         <v>0.5359130514205361</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>595</v>
+        <v>446.25</v>
       </c>
       <c r="B121" t="n">
         <v>0.5220341726029716</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B122" t="n">
         <v>0.6714112447464942</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>605</v>
+        <v>453.75</v>
       </c>
       <c r="B123" t="n">
         <v>0.7879062380549726</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>610</v>
+        <v>457.5</v>
       </c>
       <c r="B124" t="n">
         <v>0.5219106105494546</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>615</v>
+        <v>461.25</v>
       </c>
       <c r="B125" t="n">
         <v>0.4645082326565557</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>620</v>
+        <v>465</v>
       </c>
       <c r="B126" t="n">
         <v>0.4544609504359585</v>
@@ -4104,7 +4104,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>625</v>
+        <v>468.75</v>
       </c>
       <c r="B127" t="n">
         <v>0.4759504823460361</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>630</v>
+        <v>472.5</v>
       </c>
       <c r="B128" t="n">
         <v>0.4222223292995864</v>
@@ -4162,7 +4162,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>635</v>
+        <v>476.25</v>
       </c>
       <c r="B129" t="n">
         <v>0.439899936905249</v>
@@ -4191,7 +4191,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>640</v>
+        <v>480</v>
       </c>
       <c r="B130" t="n">
         <v>0.4955635949976767</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>645</v>
+        <v>483.75</v>
       </c>
       <c r="B131" t="n">
         <v>0.4086180853361867</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>650</v>
+        <v>487.5</v>
       </c>
       <c r="B132" t="n">
         <v>0.3656472133005622</v>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>655</v>
+        <v>491.25</v>
       </c>
       <c r="B133" t="n">
         <v>0.3817091389064302</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>660</v>
+        <v>495</v>
       </c>
       <c r="B134" t="n">
         <v>0.4543174905358569</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>665</v>
+        <v>498.75</v>
       </c>
       <c r="B135" t="n">
         <v>0.3780467063466944</v>
@@ -4365,7 +4365,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>670</v>
+        <v>502.5</v>
       </c>
       <c r="B136" t="n">
         <v>0.6393487700149478</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>675</v>
+        <v>506.25</v>
       </c>
       <c r="B137" t="n">
         <v>0.6972558611067825</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>680</v>
+        <v>510</v>
       </c>
       <c r="B138" t="n">
         <v>0.9166647508586294</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>685</v>
+        <v>513.75</v>
       </c>
       <c r="B139" t="n">
         <v>0.8770311407694891</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>690</v>
+        <v>517.5</v>
       </c>
       <c r="B140" t="n">
         <v>0.6362664744190596</v>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>695</v>
+        <v>521.25</v>
       </c>
       <c r="B141" t="n">
         <v>0.5367503612937838</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>700</v>
+        <v>525</v>
       </c>
       <c r="B142" t="n">
         <v>0.3680864505232933</v>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>705</v>
+        <v>528.75</v>
       </c>
       <c r="B143" t="n">
         <v>0.4067685205708216</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>710</v>
+        <v>532.5</v>
       </c>
       <c r="B144" t="n">
         <v>0.4291415494061397</v>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>715</v>
+        <v>536.25</v>
       </c>
       <c r="B145" t="n">
         <v>0.4937003314331747</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
       <c r="B146" t="n">
         <v>0.3835034879041359</v>
@@ -4684,7 +4684,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>725</v>
+        <v>543.75</v>
       </c>
       <c r="B147" t="n">
         <v>0.2688367987006615</v>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>730</v>
+        <v>547.5</v>
       </c>
       <c r="B148" t="n">
         <v>0.3569289030568967</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>735</v>
+        <v>551.25</v>
       </c>
       <c r="B149" t="n">
         <v>0.3954471448468553</v>
@@ -4771,7 +4771,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>740</v>
+        <v>555</v>
       </c>
       <c r="B150" t="n">
         <v>0.3285294282322582</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>745</v>
+        <v>558.75</v>
       </c>
       <c r="B151" t="n">
         <v>0.4769266989534202</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>750</v>
+        <v>562.5</v>
       </c>
       <c r="B152" t="n">
         <v>0.4691760481213123</v>
@@ -4858,7 +4858,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>755</v>
+        <v>566.25</v>
       </c>
       <c r="B153" t="n">
         <v>0.3452725804126544</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>760</v>
+        <v>570</v>
       </c>
       <c r="B154" t="n">
         <v>0.3587243985424209</v>
@@ -4916,7 +4916,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>765</v>
+        <v>573.75</v>
       </c>
       <c r="B155" t="n">
         <v>0.4534356115646148</v>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>770</v>
+        <v>577.5</v>
       </c>
       <c r="B156" t="n">
         <v>0.3782773150638405</v>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>775</v>
+        <v>581.25</v>
       </c>
       <c r="B157" t="n">
         <v>0.2459191258004694</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>780</v>
+        <v>585</v>
       </c>
       <c r="B158" t="n">
         <v>0.2770898180398547</v>
@@ -5032,7 +5032,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>785</v>
+        <v>588.75</v>
       </c>
       <c r="B159" t="n">
         <v>0.2827670512709091</v>
@@ -5061,7 +5061,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>790</v>
+        <v>592.5</v>
       </c>
       <c r="B160" t="n">
         <v>0.1622308300588884</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>795</v>
+        <v>596.25</v>
       </c>
       <c r="B161" t="n">
         <v>0.1984012857102471</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="B162" t="n">
         <v>0.1577425918251834</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>805</v>
+        <v>603.75</v>
       </c>
       <c r="B163" t="n">
         <v>0.2204808307033375</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>810</v>
+        <v>607.5</v>
       </c>
       <c r="B164" t="n">
         <v>0.1815014789171983</v>
@@ -5206,7 +5206,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>815</v>
+        <v>611.25</v>
       </c>
       <c r="B165" t="n">
         <v>0.01767977652204422</v>
@@ -5235,7 +5235,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>820</v>
+        <v>615</v>
       </c>
       <c r="B166" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>825</v>
+        <v>618.75</v>
       </c>
       <c r="B167" t="n">
         <v>0.2159586986534237</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>830</v>
+        <v>622.5</v>
       </c>
       <c r="B168" t="n">
         <v>0.3995712146707717</v>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>835</v>
+        <v>626.25</v>
       </c>
       <c r="B169" t="n">
         <v>0.3898181493841975</v>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="B170" t="n">
         <v>0.4090570771808189</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>845</v>
+        <v>633.75</v>
       </c>
       <c r="B171" t="n">
         <v>0.439627364916106</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>850</v>
+        <v>637.5</v>
       </c>
       <c r="B172" t="n">
         <v>0.3677636580023744</v>
@@ -5438,7 +5438,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>855</v>
+        <v>641.25</v>
       </c>
       <c r="B173" t="n">
         <v>0.4604378899490627</v>
@@ -5467,7 +5467,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>860</v>
+        <v>645</v>
       </c>
       <c r="B174" t="n">
         <v>0.3571641242376558</v>
@@ -5496,7 +5496,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>865</v>
+        <v>648.75</v>
       </c>
       <c r="B175" t="n">
         <v>0.3724553431707989</v>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>870</v>
+        <v>652.5</v>
       </c>
       <c r="B176" t="n">
         <v>0.4451810606499009</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>875</v>
+        <v>656.25</v>
       </c>
       <c r="B177" t="n">
         <v>0.625954080558401</v>
@@ -5583,7 +5583,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>880</v>
+        <v>660</v>
       </c>
       <c r="B178" t="n">
         <v>0.5208201639120063</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>885</v>
+        <v>663.75</v>
       </c>
       <c r="B179" t="n">
         <v>0.5071836828134479</v>
@@ -5641,7 +5641,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>890</v>
+        <v>667.5</v>
       </c>
       <c r="B180" t="n">
         <v>0.6479528009996187</v>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>895</v>
+        <v>671.25</v>
       </c>
       <c r="B181" t="n">
         <v>0.6803687581013804</v>
@@ -5699,7 +5699,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>900</v>
+        <v>675</v>
       </c>
       <c r="B182" t="n">
         <v>0.6654655202066948</v>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>905</v>
+        <v>678.75</v>
       </c>
       <c r="B183" t="n">
         <v>0.6797579422705979</v>
@@ -5757,7 +5757,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>910</v>
+        <v>682.5</v>
       </c>
       <c r="B184" t="n">
         <v>0.6823463390847593</v>
@@ -5786,7 +5786,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>915</v>
+        <v>686.25</v>
       </c>
       <c r="B185" t="n">
         <v>0.6466864930342808</v>
@@ -5815,7 +5815,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>920</v>
+        <v>690</v>
       </c>
       <c r="B186" t="n">
         <v>0.6980499946398169</v>
@@ -5840,7 +5840,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>925</v>
+        <v>693.75</v>
       </c>
       <c r="B187" t="n">
         <v>0.6818829560870938</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>930</v>
+        <v>697.5</v>
       </c>
       <c r="B188" t="n">
         <v>0.6651051017035741</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>935</v>
+        <v>701.25</v>
       </c>
       <c r="B189" t="n">
         <v>0.6465181836680642</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>940</v>
+        <v>705</v>
       </c>
       <c r="B190" t="n">
         <v>0.6125881061581708</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>945</v>
+        <v>708.75</v>
       </c>
       <c r="B191" t="n">
         <v>0.6243882752343808</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>950</v>
+        <v>712.5</v>
       </c>
       <c r="B192" t="n">
         <v>0.6390009346512073</v>
@@ -6014,7 +6014,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>955</v>
+        <v>716.25</v>
       </c>
       <c r="B193" t="n">
         <v>0.6280266936993968</v>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="B194" t="n">
         <v>0.6820514734184542</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>965</v>
+        <v>723.75</v>
       </c>
       <c r="B195" t="n">
         <v>0.693418464005461</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>970</v>
+        <v>727.5</v>
       </c>
       <c r="B196" t="n">
         <v>0.670515965500087</v>
@@ -6130,7 +6130,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>975</v>
+        <v>731.25</v>
       </c>
       <c r="B197" t="n">
         <v>0.6653258656014742</v>
@@ -6159,7 +6159,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>980</v>
+        <v>735</v>
       </c>
       <c r="B198" t="n">
         <v>0.6700525825024499</v>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>985</v>
+        <v>738.75</v>
       </c>
       <c r="B199" t="n">
         <v>0.6255989215689794</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>990</v>
+        <v>742.5</v>
       </c>
       <c r="B200" t="n">
         <v>0.6767451027550067</v>
@@ -6246,7 +6246,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>995</v>
+        <v>746.25</v>
       </c>
       <c r="B201" t="n">
         <v>0.6938298422368376</v>
@@ -6275,7 +6275,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="B202" t="n">
         <v>0.689418833700131</v>
@@ -6304,7 +6304,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1005</v>
+        <v>753.75</v>
       </c>
       <c r="B203" t="n">
         <v>0.6975655271439507</v>
@@ -6333,7 +6333,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1010</v>
+        <v>757.5</v>
       </c>
       <c r="B204" t="n">
         <v>0.6714427314954037</v>
@@ -6362,7 +6362,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1015</v>
+        <v>761.25</v>
       </c>
       <c r="B205" t="n">
         <v>0.6755377898676045</v>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="B206" t="n">
         <v>0.6649501324427547</v>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1025</v>
+        <v>768.75</v>
       </c>
       <c r="B207" t="n">
         <v>0.6791260419415721</v>
@@ -6449,7 +6449,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1030</v>
+        <v>772.5</v>
       </c>
       <c r="B208" t="n">
         <v>0.6658844348657311</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1035</v>
+        <v>776.25</v>
       </c>
       <c r="B209" t="n">
         <v>0.6102811661836824</v>
@@ -6507,7 +6507,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1040</v>
+        <v>780</v>
       </c>
       <c r="B210" t="n">
         <v>0.6215205465762352</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1045</v>
+        <v>783.75</v>
       </c>
       <c r="B211" t="n">
         <v>0.5422096905929834</v>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1050</v>
+        <v>787.5</v>
       </c>
       <c r="B212" t="n">
         <v>0.6717844121387628</v>
@@ -6594,7 +6594,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1055</v>
+        <v>791.25</v>
       </c>
       <c r="B213" t="n">
         <v>0.7586595191507968</v>
@@ -6623,7 +6623,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1060</v>
+        <v>795</v>
       </c>
       <c r="B214" t="n">
         <v>0.8344996645902683</v>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1065</v>
+        <v>798.75</v>
       </c>
       <c r="B215" t="n">
         <v>0.9177289347271937</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1070</v>
+        <v>802.5</v>
       </c>
       <c r="B216" t="n">
         <v>0.8145230471504448</v>
@@ -6710,7 +6710,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1075</v>
+        <v>806.25</v>
       </c>
       <c r="B217" t="n">
         <v>0.7306541552136849</v>
@@ -6739,7 +6739,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1080</v>
+        <v>810</v>
       </c>
       <c r="B218" t="n">
         <v>0.8770925987330003</v>
@@ -6768,7 +6768,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1085</v>
+        <v>813.75</v>
       </c>
       <c r="B219" t="n">
         <v>0.8367378017414069</v>
@@ -6797,7 +6797,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1090</v>
+        <v>817.5</v>
       </c>
       <c r="B220" t="n">
         <v>0.7752320400961139</v>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1095</v>
+        <v>821.25</v>
       </c>
       <c r="B221" t="n">
         <v>0.7825574386474869</v>
@@ -6855,7 +6855,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1100</v>
+        <v>825</v>
       </c>
       <c r="B222" t="n">
         <v>0.7754429823018398</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1105</v>
+        <v>828.75</v>
       </c>
       <c r="B223" t="n">
         <v>0.7811669632250897</v>
@@ -6913,7 +6913,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1110</v>
+        <v>832.5</v>
       </c>
       <c r="B224" t="n">
         <v>0.5667499352919094</v>
@@ -6942,7 +6942,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1115</v>
+        <v>836.25</v>
       </c>
       <c r="B225" t="n">
         <v>0.4853645858206619</v>
@@ -6971,7 +6971,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="B226" t="n">
         <v>0.381163462664702</v>
@@ -7000,7 +7000,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1125</v>
+        <v>843.75</v>
       </c>
       <c r="B227" t="n">
         <v>0.4326656939382048</v>
@@ -7029,7 +7029,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1130</v>
+        <v>847.5</v>
       </c>
       <c r="B228" t="n">
         <v>0.560006625939991</v>
@@ -7058,7 +7058,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1135</v>
+        <v>851.25</v>
       </c>
       <c r="B229" t="n">
         <v>0.6796105094374383</v>
@@ -7087,7 +7087,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1140</v>
+        <v>855</v>
       </c>
       <c r="B230" t="n">
         <v>0.7018811076138007</v>
@@ -7116,7 +7116,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1145</v>
+        <v>858.75</v>
       </c>
       <c r="B231" t="n">
         <v>0.6166192905568977</v>
@@ -7145,7 +7145,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1150</v>
+        <v>862.5</v>
       </c>
       <c r="B232" t="n">
         <v>0.6519075528133271</v>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1155</v>
+        <v>866.25</v>
       </c>
       <c r="B233" t="n">
         <v>0.5781447407219957</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1160</v>
+        <v>870</v>
       </c>
       <c r="B234" t="n">
         <v>0.6357977914337596</v>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1165</v>
+        <v>873.75</v>
       </c>
       <c r="B235" t="n">
         <v>0.6340469747103441</v>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1170</v>
+        <v>877.5</v>
       </c>
       <c r="B236" t="n">
         <v>0.6614214215627499</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1175</v>
+        <v>881.25</v>
       </c>
       <c r="B237" t="n">
         <v>0.6665163351947569</v>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1180</v>
+        <v>885</v>
       </c>
       <c r="B238" t="n">
         <v>0.6653180873735351</v>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1185</v>
+        <v>888.75</v>
       </c>
       <c r="B239" t="n">
         <v>0.6564713404194151</v>
@@ -7377,7 +7377,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1190</v>
+        <v>892.5</v>
       </c>
       <c r="B240" t="n">
         <v>0.5679259964849734</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1195</v>
+        <v>896.25</v>
       </c>
       <c r="B241" t="n">
         <v>0.6474703043956538</v>
@@ -7435,7 +7435,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="B242" t="n">
         <v>0.6337830512558611</v>
@@ -7464,7 +7464,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1205</v>
+        <v>903.75</v>
       </c>
       <c r="B243" t="n">
         <v>0.6996472013837689</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1210</v>
+        <v>907.5</v>
       </c>
       <c r="B244" t="n">
         <v>0.7741591043549647</v>
@@ -7522,7 +7522,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1215</v>
+        <v>911.25</v>
       </c>
       <c r="B245" t="n">
         <v>0.6968251201322886</v>
@@ -7551,7 +7551,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1220</v>
+        <v>915</v>
       </c>
       <c r="B246" t="n">
         <v>0.6427687461720524</v>
@@ -7580,7 +7580,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1225</v>
+        <v>918.75</v>
       </c>
       <c r="B247" t="n">
         <v>0.6485215568859957</v>
@@ -7609,7 +7609,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1230</v>
+        <v>922.5</v>
       </c>
       <c r="B248" t="n">
         <v>0.6340817019889755</v>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1235</v>
+        <v>926.25</v>
       </c>
       <c r="B249" t="n">
         <v>0.6268617745404583</v>
@@ -7667,7 +7667,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1240</v>
+        <v>930</v>
       </c>
       <c r="B250" t="n">
         <v>0.6449853095783027</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1245</v>
+        <v>933.75</v>
       </c>
       <c r="B251" t="n">
         <v>0.6412119231253826</v>
@@ -7725,7 +7725,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1250</v>
+        <v>937.5</v>
       </c>
       <c r="B252" t="n">
         <v>0.6236676316969891</v>
@@ -7754,7 +7754,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1255</v>
+        <v>941.25</v>
       </c>
       <c r="B253" t="n">
         <v>0.5964790663815052</v>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="B254" t="n">
         <v>0.5915096553035255</v>
@@ -7812,7 +7812,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1265</v>
+        <v>948.75</v>
       </c>
       <c r="B255" t="n">
         <v>0.589186934506813</v>
@@ -7841,7 +7841,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1270</v>
+        <v>952.5</v>
       </c>
       <c r="B256" t="n">
         <v>0.6704527712235517</v>
@@ -7870,7 +7870,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1275</v>
+        <v>956.25</v>
       </c>
       <c r="B257" t="n">
         <v>0.7321823546059392</v>
@@ -7899,7 +7899,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1280</v>
+        <v>960</v>
       </c>
       <c r="B258" t="n">
         <v>0.6561296447299867</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1285</v>
+        <v>963.75</v>
       </c>
       <c r="B259" t="n">
         <v>0.710059854823399</v>
@@ -7957,7 +7957,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1290</v>
+        <v>967.5</v>
       </c>
       <c r="B260" t="n">
         <v>0.7119610865698149</v>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1295</v>
+        <v>971.25</v>
       </c>
       <c r="B261" t="n">
         <v>0.6382852172077236</v>
@@ -8015,7 +8015,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1300</v>
+        <v>975</v>
       </c>
       <c r="B262" t="n">
         <v>0.5436910970484092</v>
@@ -8044,7 +8044,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1305</v>
+        <v>978.75</v>
       </c>
       <c r="B263" t="n">
         <v>0.4801758876106561</v>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1310</v>
+        <v>982.5</v>
       </c>
       <c r="B264" t="n">
         <v>0.6440730172453186</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1315</v>
+        <v>986.25</v>
       </c>
       <c r="B265" t="n">
         <v>0.7196867275021361</v>
@@ -8131,7 +8131,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1320</v>
+        <v>990</v>
       </c>
       <c r="B266" t="n">
         <v>0.6885229856604269</v>
@@ -8160,7 +8160,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1325</v>
+        <v>993.75</v>
       </c>
       <c r="B267" t="n">
         <v>0.5868764323407589</v>
@@ -8189,7 +8189,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1330</v>
+        <v>997.5</v>
       </c>
       <c r="B268" t="n">
         <v>0.3803514774538144</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1335</v>
+        <v>1001.25</v>
       </c>
       <c r="B269" t="n">
         <v>0.4202335004061268</v>
@@ -8247,7 +8247,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1340</v>
+        <v>1005</v>
       </c>
       <c r="B270" t="n">
         <v>0.486861911502757</v>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1345</v>
+        <v>1008.75</v>
       </c>
       <c r="B271" t="n">
         <v>0.683154866627163</v>
@@ -8305,7 +8305,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1350</v>
+        <v>1012.5</v>
       </c>
       <c r="B272" t="n">
         <v>0.4762305044511947</v>
@@ -8334,7 +8334,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1355</v>
+        <v>1016.25</v>
       </c>
       <c r="B273" t="n">
         <v>0.6461881681400428</v>
@@ -8363,7 +8363,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1360</v>
+        <v>1020</v>
       </c>
       <c r="B274" t="n">
         <v>0.6435751172132882</v>
@@ -8392,7 +8392,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1365</v>
+        <v>1023.75</v>
       </c>
       <c r="B275" t="n">
         <v>0.4501564258258952</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1370</v>
+        <v>1027.5</v>
       </c>
       <c r="B276" t="n">
         <v>0.5575003151347744</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1375</v>
+        <v>1031.25</v>
       </c>
       <c r="B277" t="n">
         <v>0.606561383614391</v>
@@ -8479,7 +8479,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1380</v>
+        <v>1035</v>
       </c>
       <c r="B278" t="n">
         <v>0.6983157222789345</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1385</v>
+        <v>1038.75</v>
       </c>
       <c r="B279" t="n">
         <v>0.6859702074899729</v>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1390</v>
+        <v>1042.5</v>
       </c>
       <c r="B280" t="n">
         <v>0.5455797560620255</v>
@@ -8566,7 +8566,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1395</v>
+        <v>1046.25</v>
       </c>
       <c r="B281" t="n">
         <v>0.4945053068867509</v>
@@ -8595,7 +8595,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1400</v>
+        <v>1050</v>
       </c>
       <c r="B282" t="n">
         <v>0.2106452616321377</v>
@@ -8624,7 +8624,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1405</v>
+        <v>1053.75</v>
       </c>
       <c r="B283" t="n">
         <v>0.3167436384750459</v>
@@ -8653,7 +8653,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1410</v>
+        <v>1057.5</v>
       </c>
       <c r="B284" t="n">
         <v>0.4215190926720283</v>
@@ -8682,7 +8682,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1415</v>
+        <v>1061.25</v>
       </c>
       <c r="B285" t="n">
         <v>0.4882587543091716</v>
@@ -8711,7 +8711,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1420</v>
+        <v>1065</v>
       </c>
       <c r="B286" t="n">
         <v>0.8412329694316156</v>
@@ -8740,7 +8740,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1425</v>
+        <v>1068.75</v>
       </c>
       <c r="B287" t="n">
         <v>0.7223296634609824</v>
@@ -8769,7 +8769,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1430</v>
+        <v>1072.5</v>
       </c>
       <c r="B288" t="n">
         <v>0.8137267953957377</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1435</v>
+        <v>1076.25</v>
       </c>
       <c r="B289" t="n">
         <v>0.8507532808853711</v>
@@ -8827,7 +8827,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="B290" t="n">
         <v>0.8429121557224732</v>
@@ -8856,7 +8856,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1445</v>
+        <v>1083.75</v>
       </c>
       <c r="B291" t="n">
         <v>0.8341177897764851</v>
@@ -8885,7 +8885,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1450</v>
+        <v>1087.5</v>
       </c>
       <c r="B292" t="n">
         <v>0.8406462320464243</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1455</v>
+        <v>1091.25</v>
       </c>
       <c r="B293" t="n">
         <v>0.7421263908493785</v>
@@ -8943,7 +8943,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>1460</v>
+        <v>1095</v>
       </c>
       <c r="B294" t="n">
         <v>0.47007699709836</v>
@@ -8972,7 +8972,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>1465</v>
+        <v>1098.75</v>
       </c>
       <c r="B295" t="n">
         <v>0.5351869522004193</v>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1470</v>
+        <v>1102.5</v>
       </c>
       <c r="B296" t="n">
         <v>0.5390370102576298</v>
@@ -9030,7 +9030,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1475</v>
+        <v>1106.25</v>
       </c>
       <c r="B297" t="n">
         <v>0.7851567503057169</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1480</v>
+        <v>1110</v>
       </c>
       <c r="B298" t="n">
         <v>0.7057029623015012</v>
@@ -9088,7 +9088,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1485</v>
+        <v>1113.75</v>
       </c>
       <c r="B299" t="n">
         <v>0.7644167352636657</v>
@@ -9117,7 +9117,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1490</v>
+        <v>1117.5</v>
       </c>
       <c r="B300" t="n">
         <v>0.7579907254716716</v>
@@ -9146,7 +9146,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1495</v>
+        <v>1121.25</v>
       </c>
       <c r="B301" t="n">
         <v>0.7815677581246234</v>
@@ -9175,7 +9175,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="B302" t="n">
         <v>0.7442010531095917</v>
@@ -9204,7 +9204,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>1505</v>
+        <v>1128.75</v>
       </c>
       <c r="B303" t="n">
         <v>0.7879717566013653</v>
@@ -9233,7 +9233,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1510</v>
+        <v>1132.5</v>
       </c>
       <c r="B304" t="n">
         <v>0.7859670345869461</v>
@@ -9262,7 +9262,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>1515</v>
+        <v>1136.25</v>
       </c>
       <c r="B305" t="n">
         <v>0.6814249489423361</v>
@@ -9291,7 +9291,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1520</v>
+        <v>1140</v>
       </c>
       <c r="B306" t="n">
         <v>0.6519451003806154</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1525</v>
+        <v>1143.75</v>
       </c>
       <c r="B307" t="n">
         <v>0.6385965161761789</v>
@@ -9349,7 +9349,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>1530</v>
+        <v>1147.5</v>
       </c>
       <c r="B308" t="n">
         <v>0.6004695911560844</v>
@@ -9378,7 +9378,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1535</v>
+        <v>1151.25</v>
       </c>
       <c r="B309" t="n">
         <v>0.5539225181673828</v>
@@ -9407,7 +9407,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1540</v>
+        <v>1155</v>
       </c>
       <c r="B310" t="n">
         <v>0.5186991593104011</v>
@@ -9436,7 +9436,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1545</v>
+        <v>1158.75</v>
       </c>
       <c r="B311" t="n">
         <v>0.5847986614834895</v>
@@ -9465,7 +9465,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>1550</v>
+        <v>1162.5</v>
       </c>
       <c r="B312" t="n">
         <v>0.5134663498169658</v>
@@ -9494,7 +9494,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1555</v>
+        <v>1166.25</v>
       </c>
       <c r="B313" t="n">
         <v>0.5884396086982946</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>1560</v>
+        <v>1170</v>
       </c>
       <c r="B314" t="n">
         <v>0.5019137684509474</v>
@@ -9552,7 +9552,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1565</v>
+        <v>1173.75</v>
       </c>
       <c r="B315" t="n">
         <v>0.4998624873461779</v>
@@ -9581,7 +9581,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1570</v>
+        <v>1177.5</v>
       </c>
       <c r="B316" t="n">
         <v>0.3461857059700861</v>
@@ -9610,7 +9610,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1575</v>
+        <v>1181.25</v>
       </c>
       <c r="B317" t="n">
         <v>0.2872960064836434</v>
@@ -9639,7 +9639,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1580</v>
+        <v>1185</v>
       </c>
       <c r="B318" t="n">
         <v>0.3537256667462856</v>
@@ -9668,7 +9668,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1585</v>
+        <v>1188.75</v>
       </c>
       <c r="B319" t="n">
         <v>0.3879306415951476</v>
@@ -9697,7 +9697,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>1590</v>
+        <v>1192.5</v>
       </c>
       <c r="B320" t="n">
         <v>0.3032798516540964</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>1595</v>
+        <v>1196.25</v>
       </c>
       <c r="B321" t="n">
         <v>0.3732612870466312</v>
@@ -9755,7 +9755,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="B322" t="n">
         <v>0.2934948224115885</v>
@@ -9784,7 +9784,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1605</v>
+        <v>1203.75</v>
       </c>
       <c r="B323" t="n">
         <v>0.4010645744310608</v>
@@ -9833,42 +9833,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Standard Deviation</t>
+          <t>std</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Kurtosis</t>
+          <t>kurtosis</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Skewness</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Zero Crossing Rate</t>
+          <t>zcr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>entropy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Band Energy (2-3 Hz)</t>
+          <t>band_energy</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Spectral Flux</t>
+          <t>spectral_flux</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="B3" t="n">
         <v>0.7192379265135571</v>
@@ -9932,7 +9932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" t="n">
         <v>0.7805961690858965</v>
@@ -9961,7 +9961,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="B5" t="n">
         <v>0.7266933116732304</v>
@@ -9990,7 +9990,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B6" t="n">
         <v>0.6431350400323055</v>
@@ -10019,7 +10019,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="B7" t="n">
         <v>0.5334093689963026</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B8" t="n">
         <v>0.5867250685819272</v>
@@ -10077,7 +10077,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>70</v>
+        <v>52.5</v>
       </c>
       <c r="B9" t="n">
         <v>0.5609766858392788</v>
@@ -10106,7 +10106,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B10" t="n">
         <v>0.6169144933096931</v>
@@ -10135,7 +10135,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>90</v>
+        <v>67.5</v>
       </c>
       <c r="B11" t="n">
         <v>0.8322673682186803</v>
@@ -10164,7 +10164,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -10193,7 +10193,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110</v>
+        <v>82.5</v>
       </c>
       <c r="B13" t="n">
         <v>0.5703488017305176</v>
@@ -10222,7 +10222,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B14" t="n">
         <v>0.2387982398647637</v>
@@ -10251,7 +10251,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130</v>
+        <v>97.5</v>
       </c>
       <c r="B15" t="n">
         <v>0.3131631195305857</v>
@@ -10280,7 +10280,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B16" t="n">
         <v>0.3620974223991311</v>
@@ -10309,7 +10309,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>150</v>
+        <v>112.5</v>
       </c>
       <c r="B17" t="n">
         <v>0.4385420161303841</v>
@@ -10338,7 +10338,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="B18" t="n">
         <v>0.850792884326637</v>
@@ -10367,7 +10367,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>170</v>
+        <v>127.5</v>
       </c>
       <c r="B19" t="n">
         <v>0.9463525531602244</v>
@@ -10396,7 +10396,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="B20" t="n">
         <v>0.760981814507204</v>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>190</v>
+        <v>142.5</v>
       </c>
       <c r="B21" t="n">
         <v>0.8002339733862129</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B22" t="n">
         <v>0.9309973515725432</v>
@@ -10483,7 +10483,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>210</v>
+        <v>157.5</v>
       </c>
       <c r="B23" t="n">
         <v>0.9942569580308458</v>
@@ -10512,7 +10512,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="B24" t="n">
         <v>0.9744697361516046</v>
@@ -10541,7 +10541,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>230</v>
+        <v>172.5</v>
       </c>
       <c r="B25" t="n">
         <v>0.947750727193295</v>
@@ -10570,7 +10570,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B26" t="n">
         <v>0.7954607431983476</v>
@@ -10599,7 +10599,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>250</v>
+        <v>187.5</v>
       </c>
       <c r="B27" t="n">
         <v>0.7988665491905493</v>
@@ -10628,7 +10628,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="B28" t="n">
         <v>0.7897478061369299</v>
@@ -10657,7 +10657,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>270</v>
+        <v>202.5</v>
       </c>
       <c r="B29" t="n">
         <v>0.815638991295188</v>
@@ -10686,7 +10686,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="B30" t="n">
         <v>0.9093704767794719</v>
@@ -10715,7 +10715,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>290</v>
+        <v>217.5</v>
       </c>
       <c r="B31" t="n">
         <v>0.8474400747022486</v>
@@ -10744,7 +10744,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B32" t="n">
         <v>0.7629192378321648</v>
@@ -10773,7 +10773,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>310</v>
+        <v>232.5</v>
       </c>
       <c r="B33" t="n">
         <v>0.7009204635402426</v>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
       <c r="B34" t="n">
         <v>0.5561490100153748</v>
@@ -10831,7 +10831,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>330</v>
+        <v>247.5</v>
       </c>
       <c r="B35" t="n">
         <v>0.3533299784631225</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>340</v>
+        <v>255</v>
       </c>
       <c r="B36" t="n">
         <v>0.4138405439175301</v>
@@ -10889,7 +10889,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>350</v>
+        <v>262.5</v>
       </c>
       <c r="B37" t="n">
         <v>0.4378420440726956</v>
@@ -10918,7 +10918,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="B38" t="n">
         <v>0.3923811628667124</v>
@@ -10947,7 +10947,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>370</v>
+        <v>277.5</v>
       </c>
       <c r="B39" t="n">
         <v>0.402095995477012</v>
@@ -10976,7 +10976,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="B40" t="n">
         <v>0.4991218305030856</v>
@@ -11005,7 +11005,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>390</v>
+        <v>292.5</v>
       </c>
       <c r="B41" t="n">
         <v>0.4497350977633232</v>
@@ -11034,7 +11034,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B42" t="n">
         <v>0.4444863000691015</v>
@@ -11063,7 +11063,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>410</v>
+        <v>307.5</v>
       </c>
       <c r="B43" t="n">
         <v>0.3858766229019608</v>
@@ -11092,7 +11092,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="B44" t="n">
         <v>0.3691471376112219</v>
@@ -11121,7 +11121,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>430</v>
+        <v>322.5</v>
       </c>
       <c r="B45" t="n">
         <v>0.3434406241947556</v>
@@ -11150,7 +11150,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="B46" t="n">
         <v>0.3659679320407321</v>
@@ -11179,7 +11179,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>450</v>
+        <v>337.5</v>
       </c>
       <c r="B47" t="n">
         <v>0.3526318939810125</v>
@@ -11208,7 +11208,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>460</v>
+        <v>345</v>
       </c>
       <c r="B48" t="n">
         <v>0.3413272016751563</v>
@@ -11237,7 +11237,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>470</v>
+        <v>352.5</v>
       </c>
       <c r="B49" t="n">
         <v>0.3746398179348347</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="B50" t="n">
         <v>0.3904021679694694</v>
@@ -11295,7 +11295,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>490</v>
+        <v>367.5</v>
       </c>
       <c r="B51" t="n">
         <v>0.3990234056310555</v>
@@ -11324,7 +11324,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="B52" t="n">
         <v>0.4029566188459057</v>
@@ -11353,7 +11353,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>510</v>
+        <v>382.5</v>
       </c>
       <c r="B53" t="n">
         <v>0.3446409225258691</v>
@@ -11382,7 +11382,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>520</v>
+        <v>390</v>
       </c>
       <c r="B54" t="n">
         <v>0.3456093991672731</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>530</v>
+        <v>397.5</v>
       </c>
       <c r="B55" t="n">
         <v>0.438582794452941</v>
@@ -11440,7 +11440,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>540</v>
+        <v>405</v>
       </c>
       <c r="B56" t="n">
         <v>0.3464482963423592</v>
@@ -11469,7 +11469,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>550</v>
+        <v>412.5</v>
       </c>
       <c r="B57" t="n">
         <v>0.4104054777547503</v>
@@ -11498,7 +11498,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>560</v>
+        <v>420</v>
       </c>
       <c r="B58" t="n">
         <v>0.4713430984191689</v>
@@ -11527,7 +11527,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>570</v>
+        <v>427.5</v>
       </c>
       <c r="B59" t="n">
         <v>0.5601007989382083</v>
@@ -11556,7 +11556,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>580</v>
+        <v>435</v>
       </c>
       <c r="B60" t="n">
         <v>0.4638345541959126</v>
@@ -11585,7 +11585,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>590</v>
+        <v>442.5</v>
       </c>
       <c r="B61" t="n">
         <v>0.4797091578351314</v>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B62" t="n">
         <v>0.6723511332976813</v>
@@ -11643,7 +11643,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>610</v>
+        <v>457.5</v>
       </c>
       <c r="B63" t="n">
         <v>0.429045729318986</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>620</v>
+        <v>465</v>
       </c>
       <c r="B64" t="n">
         <v>0.4055443716838738</v>
@@ -11701,7 +11701,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>630</v>
+        <v>472.5</v>
       </c>
       <c r="B65" t="n">
         <v>0.3724157687378522</v>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>640</v>
+        <v>480</v>
       </c>
       <c r="B66" t="n">
         <v>0.385046676384917</v>
@@ -11759,7 +11759,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>650</v>
+        <v>487.5</v>
       </c>
       <c r="B67" t="n">
         <v>0.3243540036224744</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>660</v>
+        <v>495</v>
       </c>
       <c r="B68" t="n">
         <v>0.4128097621218672</v>
@@ -11817,7 +11817,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>670</v>
+        <v>502.5</v>
       </c>
       <c r="B69" t="n">
         <v>0.7119472957258779</v>
@@ -11846,7 +11846,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>680</v>
+        <v>510</v>
       </c>
       <c r="B70" t="n">
         <v>0.8799130169930152</v>
@@ -11875,7 +11875,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>690</v>
+        <v>517.5</v>
       </c>
       <c r="B71" t="n">
         <v>0.534128846105844</v>
@@ -11904,7 +11904,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>700</v>
+        <v>525</v>
       </c>
       <c r="B72" t="n">
         <v>0.3381044962473254</v>
@@ -11933,7 +11933,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>710</v>
+        <v>532.5</v>
       </c>
       <c r="B73" t="n">
         <v>0.4123005666148458</v>
@@ -11962,7 +11962,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
       <c r="B74" t="n">
         <v>0.2616596684568577</v>
@@ -11991,7 +11991,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>730</v>
+        <v>547.5</v>
       </c>
       <c r="B75" t="n">
         <v>0.3096079183566331</v>
@@ -12020,7 +12020,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>740</v>
+        <v>555</v>
       </c>
       <c r="B76" t="n">
         <v>0.3633559950242216</v>
@@ -12049,7 +12049,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>750</v>
+        <v>562.5</v>
       </c>
       <c r="B77" t="n">
         <v>0.3495291255039632</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>760</v>
+        <v>570</v>
       </c>
       <c r="B78" t="n">
         <v>0.338772513595913</v>
@@ -12107,7 +12107,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>770</v>
+        <v>577.5</v>
       </c>
       <c r="B79" t="n">
         <v>0.2626176483916538</v>
@@ -12136,7 +12136,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>780</v>
+        <v>585</v>
       </c>
       <c r="B80" t="n">
         <v>0.1913134187738166</v>
@@ -12165,7 +12165,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>790</v>
+        <v>592.5</v>
       </c>
       <c r="B81" t="n">
         <v>0.08923240305321656</v>
@@ -12194,7 +12194,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="B82" t="n">
         <v>0.09608840325023493</v>
@@ -12223,7 +12223,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>810</v>
+        <v>607.5</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>820</v>
+        <v>615</v>
       </c>
       <c r="B84" t="n">
         <v>0.05788756955848839</v>
@@ -12281,7 +12281,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>830</v>
+        <v>622.5</v>
       </c>
       <c r="B85" t="n">
         <v>0.3431585784789206</v>
@@ -12310,7 +12310,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="B86" t="n">
         <v>0.3558312435815907</v>
@@ -12339,7 +12339,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>850</v>
+        <v>637.5</v>
       </c>
       <c r="B87" t="n">
         <v>0.3643972935522584</v>
@@ -12368,7 +12368,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>860</v>
+        <v>645</v>
       </c>
       <c r="B88" t="n">
         <v>0.30659631641565</v>
@@ -12397,7 +12397,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>870</v>
+        <v>652.5</v>
       </c>
       <c r="B89" t="n">
         <v>0.4831094289727531</v>
@@ -12426,7 +12426,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>880</v>
+        <v>660</v>
       </c>
       <c r="B90" t="n">
         <v>0.5005451595474426</v>
@@ -12455,7 +12455,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>890</v>
+        <v>667.5</v>
       </c>
       <c r="B91" t="n">
         <v>0.6367292901901322</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>900</v>
+        <v>675</v>
       </c>
       <c r="B92" t="n">
         <v>0.6543712855902868</v>
@@ -12513,7 +12513,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>910</v>
+        <v>682.5</v>
       </c>
       <c r="B93" t="n">
         <v>0.6477985129023551</v>
@@ -12542,7 +12542,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>920</v>
+        <v>690</v>
       </c>
       <c r="B94" t="n">
         <v>0.6695593416592942</v>
@@ -12571,7 +12571,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>930</v>
+        <v>697.5</v>
       </c>
       <c r="B95" t="n">
         <v>0.6336139649841073</v>
@@ -12600,7 +12600,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>940</v>
+        <v>705</v>
       </c>
       <c r="B96" t="n">
         <v>0.6100875165839881</v>
@@ -12629,7 +12629,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>950</v>
+        <v>712.5</v>
       </c>
       <c r="B97" t="n">
         <v>0.6169098221466669</v>
@@ -12658,7 +12658,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="B98" t="n">
         <v>0.6674647155379887</v>
@@ -12687,7 +12687,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>970</v>
+        <v>727.5</v>
       </c>
       <c r="B99" t="n">
         <v>0.653764894057673</v>
@@ -12716,7 +12716,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>980</v>
+        <v>735</v>
       </c>
       <c r="B100" t="n">
         <v>0.6234957971376787</v>
@@ -12745,7 +12745,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>990</v>
+        <v>742.5</v>
       </c>
       <c r="B101" t="n">
         <v>0.6666921014887208</v>
@@ -12774,7 +12774,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="B102" t="n">
         <v>0.6805714420806481</v>
@@ -12803,7 +12803,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1010</v>
+        <v>757.5</v>
       </c>
       <c r="B103" t="n">
         <v>0.6472553759535913</v>
@@ -12832,7 +12832,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="B104" t="n">
         <v>0.6495296586798105</v>
@@ -12861,7 +12861,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1030</v>
+        <v>772.5</v>
       </c>
       <c r="B105" t="n">
         <v>0.6129249211117838</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1040</v>
+        <v>780</v>
       </c>
       <c r="B106" t="n">
         <v>0.5671197163316322</v>
@@ -12919,7 +12919,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1050</v>
+        <v>787.5</v>
       </c>
       <c r="B107" t="n">
         <v>0.6972285676535108</v>
@@ -12948,7 +12948,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1060</v>
+        <v>795</v>
       </c>
       <c r="B108" t="n">
         <v>0.8585258962453963</v>
@@ -12977,7 +12977,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1070</v>
+        <v>802.5</v>
       </c>
       <c r="B109" t="n">
         <v>0.7875260582708989</v>
@@ -13006,7 +13006,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1080</v>
+        <v>810</v>
       </c>
       <c r="B110" t="n">
         <v>0.8461424031989679</v>
@@ -13035,7 +13035,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1090</v>
+        <v>817.5</v>
       </c>
       <c r="B111" t="n">
         <v>0.7550437589450638</v>
@@ -13064,7 +13064,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1100</v>
+        <v>825</v>
       </c>
       <c r="B112" t="n">
         <v>0.7588882176913501</v>
@@ -13093,7 +13093,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1110</v>
+        <v>832.5</v>
       </c>
       <c r="B113" t="n">
         <v>0.4811136902828537</v>
@@ -13122,7 +13122,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="B114" t="n">
         <v>0.3820502461007038</v>
@@ -13151,7 +13151,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1130</v>
+        <v>847.5</v>
       </c>
       <c r="B115" t="n">
         <v>0.5986061492667289</v>
@@ -13180,7 +13180,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1140</v>
+        <v>855</v>
       </c>
       <c r="B116" t="n">
         <v>0.6372609607773398</v>
@@ -13209,7 +13209,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1150</v>
+        <v>862.5</v>
       </c>
       <c r="B117" t="n">
         <v>0.5831503071298698</v>
@@ -13238,7 +13238,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1160</v>
+        <v>870</v>
       </c>
       <c r="B118" t="n">
         <v>0.6280570706774853</v>
@@ -13267,7 +13267,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1170</v>
+        <v>877.5</v>
       </c>
       <c r="B119" t="n">
         <v>0.6412392733170265</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1180</v>
+        <v>885</v>
       </c>
       <c r="B120" t="n">
         <v>0.6132120633529041</v>
@@ -13325,7 +13325,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1190</v>
+        <v>892.5</v>
       </c>
       <c r="B121" t="n">
         <v>0.5820835281281518</v>
@@ -13354,7 +13354,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="B122" t="n">
         <v>0.646555201867173</v>
@@ -13383,7 +13383,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1210</v>
+        <v>907.5</v>
       </c>
       <c r="B123" t="n">
         <v>0.7119866513363178</v>
@@ -13412,7 +13412,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1220</v>
+        <v>915</v>
       </c>
       <c r="B124" t="n">
         <v>0.6361995500933659</v>
@@ -13441,7 +13441,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1230</v>
+        <v>922.5</v>
       </c>
       <c r="B125" t="n">
         <v>0.606381846231443</v>
@@ -13470,7 +13470,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1240</v>
+        <v>930</v>
       </c>
       <c r="B126" t="n">
         <v>0.6189764640375444</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1250</v>
+        <v>937.5</v>
       </c>
       <c r="B127" t="n">
         <v>0.566762176026387</v>
@@ -13528,7 +13528,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="B128" t="n">
         <v>0.5686426402456703</v>
@@ -13557,7 +13557,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1270</v>
+        <v>952.5</v>
       </c>
       <c r="B129" t="n">
         <v>0.6703248318337387</v>
@@ -13586,7 +13586,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1280</v>
+        <v>960</v>
       </c>
       <c r="B130" t="n">
         <v>0.6705235059564529</v>
@@ -13615,7 +13615,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1290</v>
+        <v>967.5</v>
       </c>
       <c r="B131" t="n">
         <v>0.6325964268834525</v>
@@ -13644,7 +13644,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1300</v>
+        <v>975</v>
       </c>
       <c r="B132" t="n">
         <v>0.5102797921419153</v>
@@ -13673,7 +13673,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1310</v>
+        <v>982.5</v>
       </c>
       <c r="B133" t="n">
         <v>0.6477177717397495</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1320</v>
+        <v>990</v>
       </c>
       <c r="B134" t="n">
         <v>0.5581851125160853</v>
@@ -13731,7 +13731,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1330</v>
+        <v>997.5</v>
       </c>
       <c r="B135" t="n">
         <v>0.3427076219064986</v>
@@ -13760,7 +13760,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1340</v>
+        <v>1005</v>
       </c>
       <c r="B136" t="n">
         <v>0.5111820431915675</v>
@@ -13789,7 +13789,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1350</v>
+        <v>1012.5</v>
       </c>
       <c r="B137" t="n">
         <v>0.5608799175147965</v>
@@ -13818,7 +13818,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1360</v>
+        <v>1020</v>
       </c>
       <c r="B138" t="n">
         <v>0.5058065263610985</v>
@@ -13847,7 +13847,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1370</v>
+        <v>1027.5</v>
       </c>
       <c r="B139" t="n">
         <v>0.5562347114968418</v>
@@ -13876,7 +13876,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1380</v>
+        <v>1035</v>
       </c>
       <c r="B140" t="n">
         <v>0.6578715419559273</v>
@@ -13905,7 +13905,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1390</v>
+        <v>1042.5</v>
       </c>
       <c r="B141" t="n">
         <v>0.4213061274222127</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1400</v>
+        <v>1050</v>
       </c>
       <c r="B142" t="n">
         <v>0.2416518761975652</v>
@@ -13963,7 +13963,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1410</v>
+        <v>1057.5</v>
       </c>
       <c r="B143" t="n">
         <v>0.4616191634386695</v>
@@ -13992,7 +13992,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1420</v>
+        <v>1065</v>
       </c>
       <c r="B144" t="n">
         <v>0.7693574853914384</v>
@@ -14021,7 +14021,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1430</v>
+        <v>1072.5</v>
       </c>
       <c r="B145" t="n">
         <v>0.8284785514457695</v>
@@ -14050,7 +14050,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="B146" t="n">
         <v>0.8507016958435969</v>
@@ -14079,7 +14079,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1450</v>
+        <v>1087.5</v>
       </c>
       <c r="B147" t="n">
         <v>0.6945249356381424</v>
@@ -14108,7 +14108,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1460</v>
+        <v>1095</v>
       </c>
       <c r="B148" t="n">
         <v>0.4709870250040495</v>
@@ -14137,7 +14137,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1470</v>
+        <v>1102.5</v>
       </c>
       <c r="B149" t="n">
         <v>0.6162123051811221</v>
@@ -14166,7 +14166,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1480</v>
+        <v>1110</v>
       </c>
       <c r="B150" t="n">
         <v>0.7243350708077827</v>
@@ -14195,7 +14195,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1490</v>
+        <v>1117.5</v>
       </c>
       <c r="B151" t="n">
         <v>0.7576765848577196</v>
@@ -14224,7 +14224,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="B152" t="n">
         <v>0.765857746584274</v>
@@ -14253,7 +14253,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1510</v>
+        <v>1132.5</v>
       </c>
       <c r="B153" t="n">
         <v>0.6916277228595646</v>
@@ -14282,7 +14282,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1520</v>
+        <v>1140</v>
       </c>
       <c r="B154" t="n">
         <v>0.5926914355238893</v>
@@ -14311,7 +14311,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1530</v>
+        <v>1147.5</v>
       </c>
       <c r="B155" t="n">
         <v>0.5079650474733199</v>
@@ -14340,7 +14340,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1540</v>
+        <v>1155</v>
       </c>
       <c r="B156" t="n">
         <v>0.4915471370143507</v>
@@ -14369,7 +14369,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1550</v>
+        <v>1162.5</v>
       </c>
       <c r="B157" t="n">
         <v>0.4805623795513867</v>
@@ -14398,7 +14398,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1560</v>
+        <v>1170</v>
       </c>
       <c r="B158" t="n">
         <v>0.4227741995403846</v>
@@ -14427,7 +14427,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1570</v>
+        <v>1177.5</v>
       </c>
       <c r="B159" t="n">
         <v>0.2634000448633316</v>
@@ -14456,7 +14456,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1580</v>
+        <v>1185</v>
       </c>
       <c r="B160" t="n">
         <v>0.2936632226019071</v>
@@ -14485,7 +14485,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1590</v>
+        <v>1192.5</v>
       </c>
       <c r="B161" t="n">
         <v>0.2644105406855033</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="B162" t="n">
         <v>0.2981186869586026</v>
@@ -14563,42 +14563,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Standard Deviation</t>
+          <t>std</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Kurtosis</t>
+          <t>kurtosis</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Skewness</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Zero Crossing Rate</t>
+          <t>zcr</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>entropy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Band Energy (2-3 Hz)</t>
+          <t>band_energy</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Spectral Flux</t>
+          <t>spectral_flux</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="B3" t="n">
         <v>0.6331485262916345</v>
@@ -14662,7 +14662,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B4" t="n">
         <v>0.6418674535909474</v>
@@ -14691,7 +14691,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90</v>
+        <v>67.5</v>
       </c>
       <c r="B5" t="n">
         <v>0.703110327501733</v>
@@ -14720,7 +14720,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="B6" t="n">
         <v>0.2616576903578078</v>
@@ -14749,7 +14749,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>150</v>
+        <v>112.5</v>
       </c>
       <c r="B7" t="n">
         <v>0.7467539860345482</v>
@@ -14778,7 +14778,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="B8" t="n">
         <v>0.9213409500544856</v>
@@ -14807,7 +14807,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>210</v>
+        <v>157.5</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="B10" t="n">
         <v>0.8303214040083731</v>
@@ -14865,7 +14865,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>270</v>
+        <v>202.5</v>
       </c>
       <c r="B11" t="n">
         <v>0.8712500657249507</v>
@@ -14894,7 +14894,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="B12" t="n">
         <v>0.5995883954655028</v>
@@ -14923,7 +14923,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>330</v>
+        <v>247.5</v>
       </c>
       <c r="B13" t="n">
         <v>0.3671723920072765</v>
@@ -14952,7 +14952,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>360</v>
+        <v>270</v>
       </c>
       <c r="B14" t="n">
         <v>0.4164186318740093</v>
@@ -14981,7 +14981,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>390</v>
+        <v>292.5</v>
       </c>
       <c r="B15" t="n">
         <v>0.3840920013141726</v>
@@ -15010,7 +15010,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="B16" t="n">
         <v>0.3051034789729385</v>
@@ -15039,7 +15039,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>450</v>
+        <v>337.5</v>
       </c>
       <c r="B17" t="n">
         <v>0.3105520684603817</v>
@@ -15068,7 +15068,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>480</v>
+        <v>360</v>
       </c>
       <c r="B18" t="n">
         <v>0.3407799390377733</v>
@@ -15097,7 +15097,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>510</v>
+        <v>382.5</v>
       </c>
       <c r="B19" t="n">
         <v>0.3354051893371093</v>
@@ -15126,7 +15126,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>540</v>
+        <v>405</v>
       </c>
       <c r="B20" t="n">
         <v>0.395289434621958</v>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>570</v>
+        <v>427.5</v>
       </c>
       <c r="B21" t="n">
         <v>0.5478707575786643</v>
@@ -15184,7 +15184,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B22" t="n">
         <v>0.4597807689247446</v>
@@ -15213,7 +15213,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>630</v>
+        <v>472.5</v>
       </c>
       <c r="B23" t="n">
         <v>0.3069384349344659</v>
@@ -15242,7 +15242,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>660</v>
+        <v>495</v>
       </c>
       <c r="B24" t="n">
         <v>0.6232570345288195</v>
@@ -15271,7 +15271,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>690</v>
+        <v>517.5</v>
       </c>
       <c r="B25" t="n">
         <v>0.3519302728596472</v>
@@ -15300,7 +15300,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>720</v>
+        <v>540</v>
       </c>
       <c r="B26" t="n">
         <v>0.2616730521279322</v>
@@ -15329,7 +15329,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>750</v>
+        <v>562.5</v>
       </c>
       <c r="B27" t="n">
         <v>0.2316022047939441</v>
@@ -15358,7 +15358,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>780</v>
+        <v>585</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -15387,7 +15387,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>810</v>
+        <v>607.5</v>
       </c>
       <c r="B29" t="n">
         <v>0.07644827237146501</v>
@@ -15416,7 +15416,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>840</v>
+        <v>630</v>
       </c>
       <c r="B30" t="n">
         <v>0.3323292979171413</v>
@@ -15445,7 +15445,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>870</v>
+        <v>652.5</v>
       </c>
       <c r="B31" t="n">
         <v>0.5462563488217143</v>
@@ -15474,7 +15474,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>900</v>
+        <v>675</v>
       </c>
       <c r="B32" t="n">
         <v>0.6592818342560491</v>
@@ -15503,7 +15503,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>930</v>
+        <v>697.5</v>
       </c>
       <c r="B33" t="n">
         <v>0.6393269052892094</v>
@@ -15532,7 +15532,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>960</v>
+        <v>720</v>
       </c>
       <c r="B34" t="n">
         <v>0.6638189409171957</v>
@@ -15561,7 +15561,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>990</v>
+        <v>742.5</v>
       </c>
       <c r="B35" t="n">
         <v>0.6773020771966713</v>
@@ -15590,7 +15590,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1020</v>
+        <v>765</v>
       </c>
       <c r="B36" t="n">
         <v>0.627833969291558</v>
@@ -15619,7 +15619,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1050</v>
+        <v>787.5</v>
       </c>
       <c r="B37" t="n">
         <v>0.8417928849480916</v>
@@ -15648,7 +15648,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1080</v>
+        <v>810</v>
       </c>
       <c r="B38" t="n">
         <v>0.7717390609903418</v>
@@ -15677,7 +15677,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1110</v>
+        <v>832.5</v>
       </c>
       <c r="B39" t="n">
         <v>0.503779342353468</v>
@@ -15706,7 +15706,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1140</v>
+        <v>855</v>
       </c>
       <c r="B40" t="n">
         <v>0.6190652564322647</v>
@@ -15735,7 +15735,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1170</v>
+        <v>877.5</v>
       </c>
       <c r="B41" t="n">
         <v>0.6178928459398776</v>
@@ -15764,7 +15764,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="B42" t="n">
         <v>0.6614391964965307</v>
@@ -15793,7 +15793,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1230</v>
+        <v>922.5</v>
       </c>
       <c r="B43" t="n">
         <v>0.5895253684225423</v>
@@ -15822,7 +15822,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1260</v>
+        <v>945</v>
       </c>
       <c r="B44" t="n">
         <v>0.6551547605816381</v>
@@ -15851,7 +15851,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1290</v>
+        <v>967.5</v>
       </c>
       <c r="B45" t="n">
         <v>0.6148773418910309</v>
@@ -15880,7 +15880,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1320</v>
+        <v>990</v>
       </c>
       <c r="B46" t="n">
         <v>0.4827612464126645</v>
@@ -15909,7 +15909,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1350</v>
+        <v>1012.5</v>
       </c>
       <c r="B47" t="n">
         <v>0.5527888834429433</v>
@@ -15938,7 +15938,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1380</v>
+        <v>1035</v>
       </c>
       <c r="B48" t="n">
         <v>0.4146754737440546</v>
@@ -15967,7 +15967,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1410</v>
+        <v>1057.5</v>
       </c>
       <c r="B49" t="n">
         <v>0.7412661853383469</v>
@@ -15996,7 +15996,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="B50" t="n">
         <v>0.6939194210212776</v>
@@ -16025,7 +16025,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1470</v>
+        <v>1102.5</v>
       </c>
       <c r="B51" t="n">
         <v>0.730729939016868</v>
@@ -16054,7 +16054,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1500</v>
+        <v>1125</v>
       </c>
       <c r="B52" t="n">
         <v>0.6793158610042411</v>
@@ -16083,7 +16083,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1530</v>
+        <v>1147.5</v>
       </c>
       <c r="B53" t="n">
         <v>0.4830900317678726</v>
@@ -16112,7 +16112,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1560</v>
+        <v>1170</v>
       </c>
       <c r="B54" t="n">
         <v>0.2532153054923754</v>
